--- a/nessus-agent-project/Salidas_Playbooks/nessus_agent_reporte.xlsx
+++ b/nessus-agent-project/Salidas_Playbooks/nessus_agent_reporte.xlsx
@@ -434,8 +434,8 @@
   <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -543,37 +543,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>alk33-qa</t>
+          <t>opshiftbastrh9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>alk33-qa</t>
+          <t>opshiftbastrh9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.181.11.146</t>
+          <t>10.181.40.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SLES</t>
+          <t>RedHat</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Suse</t>
+          <t>RedHat</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15.7</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>11.0.1-suse15</t>
+          <t>11.0.1-el9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>[info] [agent] HostTag::getUnix: setting TAG value to '8d210b0f3f6749a584af742f064e4907'
+          <t>[info] [agent] HostTag::getUnix: setting TAG value to '107a9b4a022644e791b54c8691ae6c6f'
 [info] [agent] Successfully linked to 10.181.8.192:8834</t>
         </is>
       </c>
@@ -622,7 +622,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-07-15T14:38:04Z</t>
+          <t>2026-09-30T20:38:22Z</t>
         </is>
       </c>
     </row>
